--- a/docs/settlements_data_dictionary.xlsx
+++ b/docs/settlements_data_dictionary.xlsx
@@ -1558,11 +1558,15 @@
       <c r="A58" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>98</v>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Fishing Activity (Highest type)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Composite indicator of fishing activity, taken as the higher of the marine and inland sub-indices (0=lowest, 1=highest).</t>
+        </is>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
